--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="501">
   <si>
     <t>Filename</t>
   </si>
@@ -808,700 +808,715 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9920,0.0015,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9529,0.0002,0.0008,0.0353</t>
-  </si>
-  <si>
-    <t>0.6368,0.0004,0.0001,0.5042</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9973,0.0006,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.9455,0.0001,0.0002,0.0571</t>
+  </si>
+  <si>
+    <t>0.2135,0.0004,0.0000,0.9006</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0002,0.0002</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9739,0.0005,0.0221,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0005,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.1345,0.0022,0.9166,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0001,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.9817,0.0010,0.0140,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0053,0.9945,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9993,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.1459,0.0003,0.8899,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.0002,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0036,0.0001,0.9964,0.0001</t>
+  </si>
+  <si>
+    <t>0.0040,0.0001,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0092,0.0002,0.9903,0.0006</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0106,0.9851,0.0017,0.0015</t>
+  </si>
+  <si>
+    <t>0.9951,0.0022,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0171,0.9994,0.0072</t>
+  </si>
+  <si>
+    <t>0.0020,0.9634,0.1073,0.0006</t>
+  </si>
+  <si>
+    <t>0.9923,0.0038,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.3649,0.4939,0.0338,0.0009</t>
+  </si>
+  <si>
+    <t>0.3160,0.7762,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9952,0.0137,0.0002</t>
+  </si>
+  <si>
+    <t>0.0246,0.1144,0.8108,0.0005</t>
+  </si>
+  <si>
+    <t>0.0015,0.0002,0.9933,0.0072</t>
+  </si>
+  <si>
+    <t>0.0075,0.0035,0.9794,0.0006</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0268,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9960,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0212,0.6019,0.0063,0.7626</t>
+  </si>
+  <si>
+    <t>0.0059,0.9867,0.0024,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.9992,0.0255,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0062,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0014,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0013,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0018,0.9971,0.0007</t>
+  </si>
+  <si>
+    <t>0.4096,0.6732,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9068,0.0558,0.0210,0.0010</t>
+  </si>
+  <si>
+    <t>0.0004,0.0027,0.9995,0.0015</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9849,0.0200,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0018,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9926,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.7000,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9955,0.0001,0.0058,0.0000</t>
+  </si>
+  <si>
+    <t>0.9164,0.0001,0.1409,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.9835,0.9690,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9977,0.9834,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.6379,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.9868,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.0000,0.0032,0.9972</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0001,0.0025,0.9978</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.0007,0.9994</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.0007,0.9997</t>
+  </si>
+  <si>
+    <t>0.0003,0.9937,0.2456,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9919,0.9556,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9763,0.9944,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0171,0.9977,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9910,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.8934,0.0000</t>
+  </si>
+  <si>
+    <t>0.9959,0.0024,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0007,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.0009,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.8545,0.0004,0.0983,0.0017</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9988,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9989,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0368,0.9726,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.8305,0.0080,0.0867,0.0010</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.6931,0.1199,0.0209,0.0021</t>
+  </si>
+  <si>
+    <t>0.9173,0.0104,0.0268,0.0009</t>
+  </si>
+  <si>
+    <t>0.0031,0.0043,0.0058,0.9936</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0108,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.9611,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9340,0.0513,0.0058,0.0001</t>
+  </si>
+  <si>
+    <t>0.4241,0.5605,0.0107,0.0008</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0001,0.0023,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0008,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.5031,0.9957,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.6647,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.9872,0.0005,0.0061,0.0001</t>
+  </si>
+  <si>
+    <t>0.2587,0.0010,0.7516,0.0008</t>
+  </si>
+  <si>
+    <t>0.0014,0.0002,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.2917,0.0019,0.7311,0.0004</t>
+  </si>
+  <si>
+    <t>0.1813,0.0001,0.0000,0.9368</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0016,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0007,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9929,0.9612,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.1255,0.8986,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9951,0.0011,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.8718,0.1429,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.6258,0.0001,0.0020,0.4310</t>
+  </si>
+  <si>
+    <t>0.0003,0.0009,0.9986,0.0033</t>
+  </si>
+  <si>
+    <t>0.9876,0.0002,0.0044,0.0018</t>
+  </si>
+  <si>
+    <t>0.9950,0.0003,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.0117,0.9709,0.0182,0.0024</t>
+  </si>
+  <si>
+    <t>0.9933,0.0020,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9904,0.0003,0.0086,0.0001</t>
+  </si>
+  <si>
+    <t>0.5035,0.1044,0.0847,0.0022</t>
+  </si>
+  <si>
+    <t>0.9803,0.0006,0.0213,0.0000</t>
+  </si>
+  <si>
+    <t>0.7272,0.0073,0.2145,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9859,0.0031,0.0036,0.0033</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9613,0.0448,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.5306,0.5568,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.1433,0.8757,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.0014,0.0046,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.9825,0.0111,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9926,0.0024,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.2468,0.7834,0.0014,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9886,0.0054,0.0026,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0264,0.9973,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0528,0.9972,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.0004,0.9959,0.0001</t>
+  </si>
+  <si>
+    <t>0.0027,0.0016,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.5166,0.0110,0.2607,0.0028</t>
+  </si>
+  <si>
+    <t>0.3601,0.0011,0.6452,0.0001</t>
+  </si>
+  <si>
+    <t>0.0422,0.0274,0.8725,0.0003</t>
+  </si>
+  <si>
+    <t>0.3996,0.0055,0.5342,0.0002</t>
+  </si>
+  <si>
+    <t>0.9855,0.0008,0.0078,0.0002</t>
+  </si>
+  <si>
+    <t>0.0025,0.0011,0.9971,0.0001</t>
+  </si>
+  <si>
+    <t>0.0163,0.9846,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0154,0.9848,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0197,0.9781,0.0016,0.0014</t>
+  </si>
+  <si>
+    <t>0.8758,0.1733,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.8347,0.1907,0.0014,0.0012</t>
+  </si>
+  <si>
+    <t>0.8693,0.0935,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9962,0.0002,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.9957,0.0006,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0116,0.0084,0.9767,0.0017</t>
+  </si>
+  <si>
+    <t>0.5497,0.0005,0.5077,0.0007</t>
+  </si>
+  <si>
+    <t>0.0009,0.0012,0.9981,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.0031,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0079,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.0105,0.0012,0.9827,0.0011</t>
+  </si>
+  <si>
+    <t>0.0003,0.0016,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9954,0.0020,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9485,0.0886,0.0006,0.0000</t>
+  </si>
+  <si>
     <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9248,0.0007,0.0894,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.0085,0.9968,0.0002</t>
-  </si>
-  <si>
-    <t>0.0500,0.0002,0.9821,0.0000</t>
-  </si>
-  <si>
-    <t>0.6119,0.0003,0.5013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9848,0.0008,0.0116,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0082,0.9910,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.9988,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0560,0.0002,0.9555,0.0004</t>
-  </si>
-  <si>
-    <t>0.0047,0.0019,0.9926,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9988,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0719,0.0001,0.9610,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.2708,0.6790,0.0049,0.0009</t>
-  </si>
-  <si>
-    <t>0.7490,0.0384,0.0832,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0059,0.9996,0.0125</t>
-  </si>
-  <si>
-    <t>0.0007,0.9956,0.0109,0.0002</t>
-  </si>
-  <si>
-    <t>0.9926,0.0042,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9934,0.0035,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.8308,0.2511,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.9332,0.6090,0.0005</t>
-  </si>
-  <si>
-    <t>0.0125,0.7612,0.1118,0.0023</t>
-  </si>
-  <si>
-    <t>0.0038,0.0003,0.9925,0.0008</t>
-  </si>
-  <si>
-    <t>0.0121,0.0014,0.9798,0.0004</t>
-  </si>
-  <si>
-    <t>0.0192,0.0001,0.9834,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0021,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9976,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9996,0.0004</t>
-  </si>
-  <si>
-    <t>0.0139,0.4669,0.0024,0.9273</t>
-  </si>
-  <si>
-    <t>0.0032,0.9936,0.0055,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0162,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0123,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0014,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.1638,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
+    <t>0.9976,0.0012,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9929,0.0024,0.0019,0.0010</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0077,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0522,0.0101,0.9117,0.0006</t>
+  </si>
+  <si>
+    <t>0.9717,0.0018,0.0143,0.0010</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9998,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0312,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0165,0.0009,0.9823,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0029,0.9967,0.0012</t>
+  </si>
+  <si>
+    <t>0.9899,0.0008,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.3449,0.0001,0.7623,0.0002</t>
+  </si>
+  <si>
+    <t>0.9964,0.0001,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0020,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0069,0.0025,0.9846,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0017,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0055,0.0486,0.9314,0.0027</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0008,0.0008,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9798,0.0181,0.0022,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0010,0.9997,0.0039</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0014,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9783,0.0288,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9711,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0009,0.9987,0.0012</t>
-  </si>
-  <si>
-    <t>0.0000,0.9918,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9275,0.0001,0.1682,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0004,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9999,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9925,0.8811,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9934,0.9825,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.3526,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.7523,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.0000,0.0016,0.9978</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0074,0.9987</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0002,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0002,0.9999</t>
-  </si>
-  <si>
-    <t>0.0008,0.9780,0.3549,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9936,0.9846,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9670,0.9876,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.3350,0.9962,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.2561,0.0000</t>
-  </si>
-  <si>
-    <t>0.9963,0.0026,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9924,0.0056,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9950,0.0039,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0015,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0004,0.9980,0.0012</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.9885,0.0004,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.9974,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.9979,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.3294,0.7468,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.0327,0.0193,0.9400,0.0014</t>
-  </si>
-  <si>
-    <t>0.9884,0.0002,0.0116,0.0000</t>
-  </si>
-  <si>
-    <t>0.1472,0.6112,0.0224,0.0077</t>
-  </si>
-  <si>
-    <t>0.7873,0.0065,0.1036,0.0020</t>
-  </si>
-  <si>
-    <t>0.0017,0.0568,0.0753,0.9274</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0050,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.9906,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9994,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9451,0.0273,0.0096,0.0001</t>
-  </si>
-  <si>
-    <t>0.3100,0.7374,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0013,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0028,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.4361,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.9739,0.0002,0.0258,0.0001</t>
-  </si>
-  <si>
-    <t>0.9688,0.0002,0.0416,0.0001</t>
-  </si>
-  <si>
-    <t>0.0156,0.0001,0.9891,0.0001</t>
-  </si>
-  <si>
-    <t>0.8649,0.0005,0.1610,0.0003</t>
-  </si>
-  <si>
-    <t>0.0397,0.0000,0.0001,0.9912</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.0003,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.8717,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0019,0.9962,0.0003,0.0015</t>
-  </si>
-  <si>
-    <t>0.9975,0.0005,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.7365,0.3254,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.2615,0.0002,0.0117,0.7354</t>
-  </si>
-  <si>
-    <t>0.0008,0.0029,0.9961,0.0081</t>
-  </si>
-  <si>
-    <t>0.8834,0.0001,0.0457,0.0096</t>
-  </si>
-  <si>
-    <t>0.9968,0.0002,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.0077,0.9894,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9717,0.0145,0.0052,0.0015</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.5100,0.0772,0.1346,0.0004</t>
-  </si>
-  <si>
-    <t>0.9440,0.0027,0.0396,0.0001</t>
-  </si>
-  <si>
-    <t>0.9710,0.0148,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9920,0.0017,0.0031,0.0009</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9884,0.0097,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.8943,0.1053,0.0044,0.0001</t>
-  </si>
-  <si>
-    <t>0.8925,0.1049,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.1522,0.0275,0.8109,0.0005</t>
-  </si>
-  <si>
-    <t>0.9932,0.0039,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0011,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9798,0.0135,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9812,0.0056,0.0075,0.0011</t>
-  </si>
-  <si>
-    <t>0.0081,0.0001,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0062,0.9986,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.1360,0.9951,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.0103,0.0014,0.9883,0.0001</t>
-  </si>
-  <si>
-    <t>0.0581,0.0031,0.9527,0.0006</t>
-  </si>
-  <si>
-    <t>0.0234,0.0015,0.9638,0.0042</t>
-  </si>
-  <si>
-    <t>0.0114,0.0020,0.9837,0.0002</t>
-  </si>
-  <si>
-    <t>0.0165,0.1184,0.7718,0.0011</t>
-  </si>
-  <si>
-    <t>0.0186,0.0029,0.9771,0.0001</t>
-  </si>
-  <si>
-    <t>0.8464,0.0019,0.1141,0.0021</t>
-  </si>
-  <si>
-    <t>0.0016,0.0002,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0275,0.9718,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.0229,0.9813,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0330,0.9708,0.0011,0.0007</t>
-  </si>
-  <si>
-    <t>0.9911,0.0070,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.2038,0.8417,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9367,0.0074,0.0230,0.0008</t>
-  </si>
-  <si>
-    <t>0.9978,0.0001,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9251,0.0109,0.0195,0.0018</t>
-  </si>
-  <si>
-    <t>0.2272,0.0040,0.7991,0.0006</t>
-  </si>
-  <si>
-    <t>0.5422,0.0031,0.4348,0.0027</t>
-  </si>
-  <si>
-    <t>0.0044,0.0019,0.9930,0.0024</t>
-  </si>
-  <si>
-    <t>0.0006,0.0009,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0011,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0253,0.0026,0.9587,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0042,0.9989,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0005,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9915,0.0049,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9974,0.0017,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0009,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0104,0.0083,0.9815,0.0017</t>
-  </si>
-  <si>
-    <t>0.9126,0.0031,0.0479,0.0076</t>
-  </si>
-  <si>
-    <t>0.0013,0.0002,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9997,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0345,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0044,0.0016,0.9914,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0015,0.9983,0.0011</t>
-  </si>
-  <si>
-    <t>0.9440,0.0021,0.0252,0.0020</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0001,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0010,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0268,0.0043,0.9526,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0252,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0017,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0028,0.9971,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.0058,0.0010,0.9914,0.0006</t>
-  </si>
-  <si>
-    <t>0.0421,0.0056,0.9304,0.0011</t>
-  </si>
-  <si>
-    <t>0.0035,0.0001,0.9847,0.0210</t>
-  </si>
-  <si>
-    <t>0.9979,0.0000,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.0011,0.0013,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.0046,0.0001,0.0006,0.9980</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.7482,0.0006,0.0006,0.2497</t>
+    <t>0.0123,0.0014,0.9702,0.0042</t>
+  </si>
+  <si>
+    <t>0.0075,0.0016,0.9901,0.0007</t>
+  </si>
+  <si>
+    <t>0.0107,0.0001,0.9892,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0000,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.0019,0.0000,0.9994</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.0003,0.9995</t>
+  </si>
+  <si>
+    <t>0.4132,0.0002,0.0094,0.6085</t>
   </si>
 </sst>
 </file>
@@ -1887,7 +1902,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1901,7 +1916,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1915,7 +1930,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1929,7 +1944,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1943,7 +1958,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1957,7 +1972,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1971,7 +1986,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1985,7 +2000,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1999,7 +2014,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2013,7 +2028,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2027,7 +2042,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2041,7 +2056,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2055,7 +2070,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2069,7 +2084,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2083,7 +2098,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2097,7 +2112,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2111,7 +2126,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2125,7 +2140,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2139,7 +2154,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2153,7 +2168,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2167,7 +2182,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2181,7 +2196,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2195,7 +2210,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2209,7 +2224,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2223,7 +2238,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2237,7 +2252,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2251,7 +2266,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2265,7 +2280,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2279,7 +2294,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2293,7 +2308,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2307,7 +2322,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2321,7 +2336,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2335,7 +2350,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2349,7 +2364,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2360,10 +2375,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2374,10 +2389,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2388,10 +2403,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2402,10 +2417,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2419,7 +2434,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2433,7 +2448,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2447,7 +2462,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2461,7 +2476,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2475,7 +2490,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2489,7 +2504,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2500,10 +2515,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2517,7 +2532,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2531,7 +2546,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2545,7 +2560,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2559,7 +2574,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2573,7 +2588,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2587,7 +2602,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2601,7 +2616,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2615,7 +2630,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2629,7 +2644,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2640,10 +2655,10 @@
         <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2657,7 +2672,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2671,7 +2686,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2685,7 +2700,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2699,7 +2714,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2713,7 +2728,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2727,7 +2742,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2741,7 +2756,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2755,7 +2770,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2769,7 +2784,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2783,7 +2798,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2797,7 +2812,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2811,7 +2826,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2825,7 +2840,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>283</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2839,7 +2854,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2853,7 +2868,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2867,7 +2882,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2881,7 +2896,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2895,7 +2910,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2906,10 +2921,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2923,7 +2938,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2937,7 +2952,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2951,7 +2966,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2965,7 +2980,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2979,7 +2994,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2993,7 +3008,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3007,7 +3022,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3021,7 +3036,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3035,7 +3050,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3049,7 +3064,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3063,7 +3078,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3077,7 +3092,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3088,10 +3103,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3105,7 +3120,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3119,7 +3134,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3133,7 +3148,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3147,7 +3162,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>268</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3161,7 +3176,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3175,7 +3190,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>269</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3189,7 +3204,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3203,7 +3218,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3217,7 +3232,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>274</v>
+        <v>359</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3231,7 +3246,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3245,7 +3260,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3259,7 +3274,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3273,7 +3288,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>273</v>
+        <v>360</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3287,7 +3302,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3301,7 +3316,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3315,7 +3330,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>358</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3329,7 +3344,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3343,7 +3358,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3357,7 +3372,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3371,7 +3386,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3385,7 +3400,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3399,7 +3414,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3413,7 +3428,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3427,7 +3442,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3441,7 +3456,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>284</v>
+        <v>370</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3455,7 +3470,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3469,7 +3484,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3480,10 +3495,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3497,7 +3512,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3508,10 +3523,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3525,7 +3540,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3539,7 +3554,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3553,7 +3568,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3567,7 +3582,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3581,7 +3596,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3595,7 +3610,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3609,7 +3624,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3623,7 +3638,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3637,7 +3652,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3651,7 +3666,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>379</v>
+        <v>275</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3665,7 +3680,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3679,7 +3694,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>358</v>
+        <v>275</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3693,7 +3708,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3707,7 +3722,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3721,7 +3736,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3735,7 +3750,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>273</v>
+        <v>388</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3749,7 +3764,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3760,10 +3775,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3774,10 +3789,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3791,7 +3806,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3805,7 +3820,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3819,7 +3834,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3830,10 +3845,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3847,7 +3862,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3858,10 +3873,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3875,7 +3890,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3889,7 +3904,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3903,7 +3918,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3917,7 +3932,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3931,7 +3946,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3945,7 +3960,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3959,7 +3974,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3973,7 +3988,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3987,7 +4002,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4001,7 +4016,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4012,10 +4027,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4029,7 +4044,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4043,7 +4058,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4057,7 +4072,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4071,7 +4086,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4085,7 +4100,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4099,7 +4114,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4113,7 +4128,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4127,7 +4142,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4141,7 +4156,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4155,7 +4170,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4169,7 +4184,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4183,7 +4198,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>358</v>
+        <v>418</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4197,7 +4212,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4211,7 +4226,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4225,7 +4240,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>356</v>
+        <v>421</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4239,7 +4254,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4253,7 +4268,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>354</v>
+        <v>423</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4267,7 +4282,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4281,7 +4296,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4292,10 +4307,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D174" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4306,10 +4321,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4323,7 +4338,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4337,7 +4352,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4351,7 +4366,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4365,7 +4380,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4376,10 +4391,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4393,7 +4408,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4407,7 +4422,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4421,7 +4436,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4435,7 +4450,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4449,7 +4464,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4463,7 +4478,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4477,7 +4492,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>431</v>
+        <v>318</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4491,7 +4506,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4505,7 +4520,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4519,7 +4534,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4533,7 +4548,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4544,10 +4559,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4561,7 +4576,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4575,7 +4590,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4589,7 +4604,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4603,7 +4618,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4617,7 +4632,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4631,7 +4646,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4645,7 +4660,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4659,7 +4674,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4673,7 +4688,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4684,10 +4699,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4701,7 +4716,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4715,7 +4730,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4729,7 +4744,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4743,7 +4758,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4754,10 +4769,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D207" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4771,7 +4786,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4785,7 +4800,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4799,7 +4814,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4813,7 +4828,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4827,7 +4842,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4841,7 +4856,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4855,7 +4870,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4869,7 +4884,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4883,7 +4898,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4897,7 +4912,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4911,7 +4926,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4925,7 +4940,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4939,7 +4954,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>273</v>
+        <v>470</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4953,7 +4968,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4967,7 +4982,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4981,7 +4996,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4995,7 +5010,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5009,7 +5024,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5023,7 +5038,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5037,7 +5052,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>314</v>
+        <v>434</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5051,7 +5066,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5065,7 +5080,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5079,7 +5094,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5093,7 +5108,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5107,7 +5122,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5121,7 +5136,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5135,7 +5150,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5149,7 +5164,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5163,7 +5178,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5177,7 +5192,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>379</v>
+        <v>486</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5191,7 +5206,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5205,7 +5220,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>358</v>
+        <v>275</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5219,7 +5234,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5233,7 +5248,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5247,7 +5262,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>482</v>
+        <v>277</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5261,7 +5276,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5275,7 +5290,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5289,7 +5304,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5303,7 +5318,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5317,7 +5332,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5331,7 +5346,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5345,7 +5360,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5359,7 +5374,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5373,7 +5388,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5387,7 +5402,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5401,7 +5416,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5415,7 +5430,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>494</v>
+        <v>399</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5429,7 +5444,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5440,10 +5455,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
